--- a/data/statistics.xlsx
+++ b/data/statistics.xlsx
@@ -428,7 +428,7 @@
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
@@ -483,11 +483,13 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>7/43 %</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>93.3</v>
+          <t>7/43</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -513,11 +515,13 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2/43 %</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>80</v>
+          <t>2/43</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -543,11 +547,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43/43 %</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>76.2</v>
+          <t>43/43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>76.2%</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -573,11 +579,13 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43/43 %</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>88.90000000000001</v>
+          <t>43/43</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -603,11 +611,13 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7/43 %</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>82.2</v>
+          <t>7/43</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82.2%</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -633,11 +643,13 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6/43 %</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>93.3</v>
+          <t>6/43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -663,11 +675,13 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2/43 %</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>100</v>
+          <t>2/43</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -693,11 +707,13 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42/43 %</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>82.90000000000001</v>
+          <t>42/43</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82.9%</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -723,15 +739,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7/43 %</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>26.7</v>
+          <t>43/43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Попытка не завершена</t>
+          <t>06.06.2026</t>
         </is>
       </c>
     </row>
@@ -753,11 +771,13 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1/43 %</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>100</v>
+          <t>1/43</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -783,11 +803,13 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7/43 %</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>91.09999999999999</v>
+          <t>7/43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>91.1%</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -813,11 +835,13 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43/43 %</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>89.8</v>
+          <t>43/43</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>89.8%</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -843,11 +867,13 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>43/43 %</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>80</v>
+          <t>43/43</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
